--- a/D-00001/operation-mapping_D-00001.xlsx
+++ b/D-00001/operation-mapping_D-00001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\iniciativas\D-00001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC71EEFF-9D05-413D-8039-7E40FA405952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B91415F-4470-43EB-A94D-A31B7449DD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,9 +48,6 @@
     <t>Descripcion del Endpoint</t>
   </si>
   <si>
-    <t>API UX UBAG Test API V1</t>
-  </si>
-  <si>
     <t>UBAG</t>
   </si>
   <si>
@@ -67,6 +64,9 @@
   </si>
   <si>
     <t>Consultar el detalle de una cuenta</t>
+  </si>
+  <si>
+    <t>API UX UBAG Customer Offer API V1</t>
   </si>
 </sst>
 </file>
@@ -102,8 +102,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,7 +385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.109375" customWidth="1"/>
@@ -416,28 +417,32 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>